--- a/ppt_engine/templates/solution_fixed_modules/M3表格模板/现场勘查情况.xlsx
+++ b/ppt_engine/templates/solution_fixed_modules/M3表格模板/现场勘查情况.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\中驰股份\材料\模板（5.26）\表格模板\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\中驰股份\PPT售前助手\材料\模板（5.26）\M3表格模板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530126FE-4D74-4FD1-BFB5-0FE56E0927D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026A544F-BA3B-44F3-ACD8-B43B7328B00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,54 +25,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>勘察小结</t>
   </si>
   <si>
-    <t>序号</t>
+    <t>施工环境与物理条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>内容</t>
+    <t>周边环境与敏感点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>对本项目的影响</t>
+    <t>安全情况与施工环保</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>材料上桥点</t>
+    <t>工期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>材料上桥需满足车辆直接进入轨行条件，目前计划4个车辆进出轨行路口，和材料堆放场地</t>
-  </si>
-  <si>
-    <t>轨行区工作面</t>
-  </si>
-  <si>
-    <t>现场全线有轨道、渣石、接触网，</t>
-  </si>
-  <si>
-    <t>装配化场地</t>
-  </si>
-  <si>
-    <t>来广营北路和中东路口做装配化场地</t>
-  </si>
-  <si>
-    <t>施工条件</t>
-  </si>
-  <si>
-    <t>与13号线间距约14.04m～50.72m，</t>
-  </si>
-  <si>
-    <t>声屏障施工跨饶</t>
-  </si>
-  <si>
-    <t>框架梁封闭式声屏障跨饶交通道路，需要做好临边防护</t>
-  </si>
-  <si>
-    <t>安全防护</t>
-  </si>
-  <si>
-    <t>临近13号线，施工过程中需注意防倾覆、防飞絮，防止人员进入营业线和吊装作业</t>
+    <t>物流限行与人员后勤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -88,11 +63,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="16"/>
@@ -101,21 +91,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -132,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -141,80 +116,41 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -222,37 +158,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,119 +455,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="22.4140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="79.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="20" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5"/>
-      <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" ht="79" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:2" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:2" ht="69.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="33.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="5" spans="1:2" ht="34" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" spans="1:2" ht="62" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
-        <v>2</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="10"/>
-    </row>
-    <row r="6" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="10"/>
-    </row>
-    <row r="9" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="B6" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C4:C5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>